--- a/Result/checksun_type/導線架.xlsx
+++ b/Result/checksun_type/導線架.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.41</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>90702033.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>105746633.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>105746633</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>142323916.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>283181158.2</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>283181158.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-35659135.80271852</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>90702033</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>90702033.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>44.26000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>87525673.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>110801500.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>110801500.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>189373875.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>283370598.82</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>283370598.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-35489764.01778525</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>87525673</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>87525673.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>44.24999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>43.64</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>128580046.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>123016262.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>123016262.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>222414981.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>283171455.62</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>283171455.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-33639988.4672454</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>128580046</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>128580046.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>44.57</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>45.41</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>43.59</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>43.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>113653630.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>135354845.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>135354845.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>226837017.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>282518805.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>282518805.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-34194706.62835827</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>113653630</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>113653630.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.91</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>43.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>108271783.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>145615587.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>145615587.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>232423142.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>281761516.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>281761516.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-32166662.7646496</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>108271783</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>108271783.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>45.24</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>43.46</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>115976369.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>178901199.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>178901199.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>246879753.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>282984175.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>282984175.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-27544021.3963283</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>115976369</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>115976369.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>45.97</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>43.39</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>43.39</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>148599483.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>267946251.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>267946251.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>246572505.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>282049366.78</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>282049366.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-20782024.32028615</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>148599483</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>148599483.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>46.44</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>45.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>43.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>190272964.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321813700.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321813700.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>247253736.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>280836529.52</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>280836529.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-13875146.98593</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>190272964</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>190272964.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>46.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>45.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>43.23</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>164957337.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>318319189.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>318319189.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>250999781.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>282811790.16</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>282811790.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-7977654.223066568</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>164957337</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>164957337.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>46.52</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>45.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>274699843.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>319230697.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>319230697.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>284091819.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>289666457.52</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>289666457.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3444640.267562151</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>274699843</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>274699843.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>46.35</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>45.14</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>43.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>43.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>561201630.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>314858307.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>314858307.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>295191794.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>297124608.34</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>297124608.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>7881055.316047311</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>561201630</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>561201630.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>43.37</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>43.42</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>39.26</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>39.26</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>194671.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>249710.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>249710</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>356270.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>295060.88</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>295060.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-48986.22120483161</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>194671</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>194671.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>44.35</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>43.32</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>39.13</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>39.13</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>268924.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>276869.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>276869.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>469712.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>292094.02</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>292094.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-41015.67804224946</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>268924</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>268924.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>45.17</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>43.18</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>38.99</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38.99</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>191081.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>301075.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>301075.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>560100.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>287452.76</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>287452.76</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-36120.02073705173</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>191081</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>191081.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>45.63</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.93</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38.8</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>304039.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>350198.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>350198.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>596125.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>284059.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>284059</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-19495.90241758886</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>304039</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>304039.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>46.11</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>38.62</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38.62</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>289835.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>357605.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>357605.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>617755.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>278555.22</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>278555.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-7153.522589156521</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>289835</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>289835.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>46.21</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>330470.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>462830.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>462830.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>662053.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>273226.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>273226.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>12255.78868678806</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>330470</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>330470.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>46.55</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>38.14</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38.14</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>389954.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>662555.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>662555</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>650777.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>267541.06</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>267541.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>35191.91948503803</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>389954</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>389954.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>46.71</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>37.91</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>436694.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>819124.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>819124.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>652349.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>260389.32</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>260389.32</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>60327.68064378656</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>436694</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>436694.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>46.08</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>37.66</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>37.66</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>341076.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>842053.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>842053.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>660817.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>252510.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>252510.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>89073.49370472052</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>341076</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>341076.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>45.12</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>37.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>815959.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>877906.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>877906</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>687531.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>246831.48</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>246831.48</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>137202.530445172</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>815959</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>815959.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>44.05</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>40.14</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>37.15</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1329092.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>861275.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>861275.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>626097.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>231467.12</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>231467.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>150177.8854156323</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1329092</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1329092.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>51.13</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>51.4</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>12954777.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>12646130.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>12646130.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>15859496.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>23078877.78</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>23078877.78</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-2857029.909741985</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>12954777</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>12954777.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>51.17</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>51.28</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>51.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>12985300.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>12710535.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>12710535.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>19914675.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22988276.62</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22988276.62</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-2985477.692602381</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>12985300</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>12985300.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>51.55</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>52.72</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>51.18</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>51.18</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>8569491.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>13726114.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>13726114.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>21988278.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>22895817.04</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>22895817.04</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3065620.643381435</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>8569491</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>8569491.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>52.16</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>52.85</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>51.12</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>51.12</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>13884265.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>14186891.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>14186891.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>22207325.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>22884126.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>22884126</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2597501.728659321</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>13884265</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>13884265.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>52.52</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>52.89</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>51.05</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>51.05</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>14836821.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>15546187.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>15546187</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>22259018.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>22705516.94</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>22705516.94</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-2405432.574461322</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>14836821</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>14836821.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>52.88</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>52.89</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>50.97</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>50.97</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>13276800.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>19072862.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>19072862</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>22607241.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>22542482.68</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>22542482.68</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-2147199.333661988</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>13276800</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>13276800.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>53.38</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>50.9</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>18063194.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>27118816.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>27118816.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>23014442.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>22409831.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>22409831.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1534463.906317867</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>18063194</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>18063194.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>53.46</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>52.78</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>50.81</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>50.81</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>10873376.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>30250442.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>30250442.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>26301473.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>22199472.58</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>22199472.58</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1117153.227743492</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>10873376</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>10873376.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>52.68</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>50.7</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>20680744.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>30227760.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>30227760.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>29549211.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>22071779.6</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>22071779.6</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>289240.8569250293</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>20680744</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>20680744.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>52.88</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>50.56</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>32470196.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>28971850.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>28971850</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>31602742.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21764283.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21764283.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>1237255.804418452</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>32470196</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>32470196.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>52.46</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>52.39</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>50.42</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>50.42</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>53506571.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>26141621.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>26141621.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>29897443.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21285267.42</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21285267.42</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1284219.593536969</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>53506571</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>53506571.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>2607.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>2356.25</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>2316.9</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>2356.25</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2316.9</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2677758350.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>4726916968.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>4726916968</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>6605213302.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>4517388635.14</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>4517388635.14</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-218348451.7329836</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2677758350</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2677758350.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>2570.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>2330.25</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>2313.3</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>2330.25</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2313.3</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>3647766645.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>4921572421.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>4921572421</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>6638005550.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>4578701974.54</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>4578701974.54</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-13678921.97781277</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>3647766645</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>3647766645.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>2549.0</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>2308.75</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>2311.5</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>2308.75</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2311.5</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4640892845.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5206842612.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5206842612</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6654623790.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>4577495022.74</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>4577495022.74</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>175265193.2787828</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4640892845</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4640892845.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>2539.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>2285.25</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>2308.5</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>2285.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2308.5</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>5025527450.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>5856816722.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>5856816722</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>6771890127.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>4565876310.44</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>4565876310.44</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>332519508.1711054</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>5025527450</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>5025527450.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>2546.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>2268.0</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>2306.7</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>2268</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2306.7</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>7642639550.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>7016893624.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>7016893624</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>6695865706.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>4561984408.04</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>4561984408.04</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>504081982.1897402</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>7642639550</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>7642639550.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>2510.0</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>2247.0</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>2301.8</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>2247</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2301.8</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>3651035615.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>8483509636.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>8483509636</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>6605332206.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>4547870940.94</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>4547870940.94</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>450763434.9953003</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3651035615</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3651035615.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>2473.0</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>2236.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>2301.5</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>2236.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2301.5</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>5074117600.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>8354438680.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>8354438680.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>6574040839.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>4593730931.24</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>4593730931.24</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>786167237.931982</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>5074117600</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>5074117600.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>2417.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>2225.25</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>2296.0</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>2225.25</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2296</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>7890763395.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>8102404969.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>8102404969.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>6526067208.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>4575039528.14</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>4575039528.14</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>1084765056.665385</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>7890763395</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>7890763395.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>2352.0</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>2209.25</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>2287.6</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>2209.25</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>2287.6</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>10825911960.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>7686963532.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>7686963532.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>5891748524.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>4533495180.54</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>4533495180.54</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>1170808281.93934</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>10825911960</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>10825911960.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>2272.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>2197.25</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>2280.1</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>2197.25</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2280.1</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>14975719610.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>6374837788.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>6374837788.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4999539713.2</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>4492817315.24</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>4492817315.24</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>937432390.2971554</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>14975719610</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>14975719610.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>2215.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>2193.0</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>2272.5</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>2193</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>2272.5</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3005680837.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>4727154777.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>4727154777.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3827769027.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>4281079047.54</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>4281079047.54</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>125936282.9405656</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3005680837</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3005680837.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>51.21</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>53.08</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>57.02</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>18202.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>9349.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>9349.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>7989.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>13460.24</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>13460.24</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>500.6753961315808</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>18202</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>18202.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>50.71</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>53.27</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>57.18</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>57.18</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>17036.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6987.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6987.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>6636.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>14299.4</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>14299.4</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-325.7147088748216</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>17036</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>17036.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>50.42999999999999</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>53.55</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>57.46</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2323.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>4899.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>4899.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6022.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>15417.3</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>15417.3</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1369.710762138438</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2323</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2323.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>50.73</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>53.94</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>57.69</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>3535.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>5598.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>5598</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6458.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>15662.04</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>15662.04</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1235.822596724375</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>3535</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>3535.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>51.26000000000001</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>54.33</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>57.9</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>5651.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>6317.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>6317.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>7375.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>15916.1</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>15916.1</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1130.274410535557</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>5651</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>5651.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>58.1</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>6391.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>6629.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>6629.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>7233.5</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>16143.36</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>16143.36</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1165.838629889547</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>6391</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>6391.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>52.62</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>58.29</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>58.29</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6596.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>6285.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>6285.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>7319.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>16730.98</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>16730.98</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-1254.293277899191</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6596</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6596.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>53.27999999999999</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>55.51</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>58.53</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>58.53</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>5817.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>7145.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>7145.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>7601.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>17385.02</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>17385.02</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-1357.825157987996</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>5817</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>5817.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>53.73999999999999</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>55.81</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>58.76</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>7133.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>7319.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>7319.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>7839.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>19212.02</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>19212.02</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-1373.769802472432</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>7133</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>7133.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>53.96</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>56.14</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>59.1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>7209.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>8433.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>8433</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>7485.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>23000.42</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>23000.42</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-1488.484658790469</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>7209</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>7209.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>53.86</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>56.38</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>59.37</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>4672.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>7837.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>7837.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>8182.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>23577.74</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>23577.74</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-1607.345715716578</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>4672</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>4672.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>65.28</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>64.45</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>890.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1040.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1040.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1629.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1306.26</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1306.26</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-83.95071200320331</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>890</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>890.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>64.58</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>64.34</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1312.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1312.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1731.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1324.24</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1324.24</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-47.41929502427229</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>69</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>64.02000000000001</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>64.23</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>64.47</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>64.47</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>2341.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1845.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1845.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1782.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1386.18</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1386.18</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>94.42627548221026</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2341</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2341.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>63.5</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1135.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>2358.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>2358</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1797.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1366.6</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1366.6</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>50.26186636710622</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1135</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1135.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>63.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>766.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>2282.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>2282.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1723.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1383.56</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1383.56</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>114.589072403847</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>766</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>766.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>63.25999999999999</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>64.06</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>64.41</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>64.41</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2250.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>2218.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>2218.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1734.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1409.4</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1409.4</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>241.9283284419107</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2250</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2250.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>63.22000000000001</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>64.07</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>64.41</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>64.41</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2737.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>2150.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>2150.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1645.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1399.08</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1399.08</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>256.2012539090763</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2737</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2737.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>63.32000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>4902.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1719.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1719.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1444.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1359.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1359.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>215.2625312225603</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>4902</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>4902.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>63.34</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>64.12</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>757.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1236.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1236.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1032.5</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1312.6</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1312.6</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-82.87359158755407</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>757</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>757.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>63.84</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1163.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1163.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1022.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1382.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1382.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-61.71542447387628</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>446</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>64.18</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>64.47</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>64.47</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1912.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1249.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1249.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1085.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1402.54</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1402.54</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>4.036079419730413</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1912</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1912.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>93.32000000000001</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>84.34</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>82.11</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>82.11</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1669171532.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>2109034871.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>2109034871</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>2389980036.4</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>806215944.92</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>806215944.92</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>190021375.3061106</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1669171532</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1669171532.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>94.44</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>83.43</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>81.84</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>81.84</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1550468237.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>2102389237.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>2102389237</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>2449074235.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>781250293.74</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>781250293.74</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>249345789.4604616</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1550468237</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1550468237.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>96.08</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>82.64</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>81.6</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>81.59999999999999</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>2134918299.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>2647793196.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>2647793196.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>2360851060.0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>757403523.54</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>757403523.54</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>337907955.9502323</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>2134918299</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>2134918299.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>98.2</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>82.13</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>81.46</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>82.13</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>81.45999999999999</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>2211360019.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>2410329446.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>2410329446.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>2160413421.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>726968976.14</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>726968976.14</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>389737545.8659678</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>2211360019</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>2211360019.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>98.34</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>81.3</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>2979256268.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>2763516105.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>2763516105.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1954659722.9</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>697717847.56</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>697717847.5599999</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>441670434.8218055</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>2979256268</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>2979256268.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>97.0</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>80.52</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>80.98999999999999</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1635943362.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>2670925201.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>2670925201.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1666618865.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>679705199.44</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>679705199.4400001</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>417811733.9793661</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1635943362</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1635943362.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>93.92</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>80.57</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>80.56999999999999</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>4277488035.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>2795759234.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>2795759234</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1517673524.5</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>662082203.66</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>662082203.66</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>512732410.7766185</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>4277488035</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>4277488035.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>88.92</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>80.04</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>80.04000000000001</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>947599549.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>2073908923.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>2073908923.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1104139823.7</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>578374274.78</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>578374274.78</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>346998862.2806711</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>947599549</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>947599549.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>82.82000000000001</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>77.26</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>79.53</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>79.53</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>3977293312.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1910497396.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1910497396.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1019461665.0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>563940432.28</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>563940432.28</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>454617599.9907224</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>3977293312</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>3977293312.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>78.46000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>76.68</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>79.19</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>79.19</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2516301751.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1145803340.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1145803340.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>630650422.0</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>490504221.4</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>490504221.4</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>267512264.9696983</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2516301751</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2516301751.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>74.34</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>76.15</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>78.93</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>78.93000000000001</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>2260113523.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>662312528.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>662312528.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>401790138.7</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>444360493.84</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>444360493.84</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>147199729.8693178</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>2260113523</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>2260113523.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>3847834.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1895258.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1895258.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1471399.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2167598.64</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2167598.64</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>128725.1200794668</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>3847834</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>3847834.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>1233198.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1369663.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1369663.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1363475.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2148522.86</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2148522.86</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-64816.37283714046</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>1233198</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>1233198.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1932137.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1292743.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1292743</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1286115.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2147117.6</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2147117.6</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-58849.77797382418</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1932137</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1932137.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1146463.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1259223.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1259223.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1347515.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2123313.92</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2123313.92</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-123110.6146700217</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1146463</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1146463.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>19.51</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1316660.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1103917.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1103917</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1374269.5</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2138601.12</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2138601.12</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-126335.6451406602</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1316660</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1316660.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>19.62</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1219860.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1047540.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1047540.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1310455.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2150367.64</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2150367.64</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-144666.2370579774</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1219860</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1219860.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>19.78</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>848595.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1357286.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1357286.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1330086.2</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2135168.2</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2135168.2</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-155314.7170449309</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>848595</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>848595.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>19.85</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>20.08</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>20.16</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1764538.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1279488.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1279488.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1676457.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2144303.58</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2144303.58</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-125201.4842746884</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1764538</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1764538.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>369932.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1435808.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1435808.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1636380.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2147606.34</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2147606.34</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-175847.8487359602</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>369932</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>369932.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>1034779.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1644622.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1644622</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1680797.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2162187.9</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2162187.9</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-92497.44622577867</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>1034779</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>1034779.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>2768590.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1573370.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1573370.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1650880.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2155087.0</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2155087</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-41355.5695603129</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>2768590</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>2768590.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>79.64</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>83.99</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>83.05</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>83.05</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>58258727.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>81634455.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>81634455.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>115083497.7</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>204090725.46</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>204090725.46</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-38089682.98646478</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>58258727</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>58258727.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>79.4</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>83.04</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>83.04000000000001</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>81486955.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>95253568.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>95253568</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>120220207.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>204953686.3</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>204953686.3</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-37800491.22076954</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>81486955</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>81486955.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>79.6</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>85.24</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>83.06</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>83.06</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>56008713.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>111419359.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>111419359</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>124660268.7</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>205224740.4</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>205224740.4</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-38526081.29760599</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>56008713</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>56008713.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>80.7</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>83.11</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>83.11</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>136796456.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>121653884.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>121653884.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>138697684.0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>207198587.04</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>207198587.04</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-35456895.43245786</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>136796456</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>136796456.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>81.75999999999999</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>83.23</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>83.23</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>75621428.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>124505003.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>124505003.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>195809999.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>206431973.26</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>206431973.26</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-38461856.10965845</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>75621428</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>75621428.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>82.78</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>86.07</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>83.28</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>126354288.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>148532539.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>148532539.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>204680045.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>207317223.06</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>207317223.06</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-34826552.0731715</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>126354288</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>126354288.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>84.16</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>86.39</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>83.37</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>83.37</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>162315910.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>145186847.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>145186847</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>213570329.2</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>220085335.38</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>220085335.38</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-33825118.73271975</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>162315910</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>162315910.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>85.05999999999999</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>86.45</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>83.58</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>83.58</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>107181340.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>137901178.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>137901178.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>217862538.3</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>226493478.0</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>226493478</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-35039490.64876297</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>107181340</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>107181340.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>85.02</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>86.29</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>83.63</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>83.63</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>151052050.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>155741483.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>155741483.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>226422553.1</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>226666785.26</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>226666785.26</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-29615621.93422604</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>151052050</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>151052050.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>85.74000000000001</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>86.51</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>83.7</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>83.7</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>195759110.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>267114996.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>267114996.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>239111235.3</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>227583931.9</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>227583931.9</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-25509970.48723665</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>195759110</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>195759110.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>86.28</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>86.18</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>83.75</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>83.75</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>109625825.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>260827551.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>260827551</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>253931033.1</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>228805701.34</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>228805701.34</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-23523725.90270764</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>109625825</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>109625825.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
